--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6EE6CC-D3AE-4292-A4A2-98B141CA1896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BED1F8-692F-407A-94A8-F558374C2374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12,12 +12,23 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="139">
   <si>
     <t>SL NO</t>
   </si>
@@ -49,124 +60,391 @@
     <t>TIME</t>
   </si>
   <si>
-    <t>ABU BAKKAR</t>
-  </si>
-  <si>
-    <t>A21784480</t>
-  </si>
-  <si>
-    <t>AFFAN CHOWDHURY UDOY</t>
-  </si>
-  <si>
-    <t>A13502392</t>
-  </si>
-  <si>
-    <t>AL ADIB HOWLADAR</t>
-  </si>
-  <si>
-    <t>A20691684</t>
-  </si>
-  <si>
-    <t>AL RABBI</t>
-  </si>
-  <si>
-    <t>A05636936</t>
-  </si>
-  <si>
-    <t>AMIR BABUCI</t>
-  </si>
-  <si>
-    <t>A16357151</t>
-  </si>
-  <si>
-    <t>ANISUR RAHMAN</t>
-  </si>
-  <si>
-    <t>A11224773</t>
-  </si>
-  <si>
-    <t>MD TOUKIR HOSSEN</t>
-  </si>
-  <si>
-    <t>A06282115</t>
-  </si>
-  <si>
-    <t>ARAFAT AHMED TANIN</t>
-  </si>
-  <si>
-    <t>A21562659</t>
-  </si>
-  <si>
-    <t>ARAFAT HOSSAIN</t>
-  </si>
-  <si>
-    <t>A00316766</t>
-  </si>
-  <si>
-    <t>ASADUZZAMAN SHUHAG</t>
-  </si>
-  <si>
-    <t>A19808967</t>
-  </si>
-  <si>
-    <t>ANOWAR MIRDHA</t>
-  </si>
-  <si>
-    <t>MIRJAN BEGUM</t>
-  </si>
-  <si>
-    <t>MOHAMMAD ATIQUR RAHMAN</t>
-  </si>
-  <si>
-    <t>MST RUMA AKTHER</t>
-  </si>
-  <si>
-    <t>MD SHAMSUL HAQUE HOWLADAR</t>
-  </si>
-  <si>
-    <t>RIKTA SARDAR</t>
-  </si>
-  <si>
-    <t>MD SHOHIDUL ISLAM</t>
-  </si>
-  <si>
-    <t>MST PERVIN AKTER</t>
-  </si>
-  <si>
-    <t>KALU BABUCI</t>
-  </si>
-  <si>
-    <t>HONUFA BEGUM</t>
-  </si>
-  <si>
-    <t>ABDUR RAHIM</t>
-  </si>
-  <si>
-    <t>TAHAMINA BEGUM</t>
-  </si>
-  <si>
-    <t>MD AKTER HOSSEN</t>
-  </si>
-  <si>
-    <t>PARUL AKTER</t>
-  </si>
-  <si>
-    <t>ABU THAHER</t>
-  </si>
-  <si>
-    <t>ASMA KHATUN</t>
-  </si>
-  <si>
-    <t>JASIM UDDIN</t>
-  </si>
-  <si>
-    <t>JASNA AKTER</t>
-  </si>
-  <si>
-    <t>ANOWAR HOSSAIN</t>
-  </si>
-  <si>
-    <t>ASMA BEGUM</t>
+    <t>MAMUN HOSEN</t>
+  </si>
+  <si>
+    <t>A07504029</t>
+  </si>
+  <si>
+    <t>RAYHAN KHAN</t>
+  </si>
+  <si>
+    <t>A07322494</t>
+  </si>
+  <si>
+    <t>MD NAJIM UDDIN</t>
+  </si>
+  <si>
+    <t>A03131255</t>
+  </si>
+  <si>
+    <t>RAKIBUL HASAN</t>
+  </si>
+  <si>
+    <t>A16817519</t>
+  </si>
+  <si>
+    <t>SUMON AHMED</t>
+  </si>
+  <si>
+    <t>A03349685</t>
+  </si>
+  <si>
+    <t>MD SABUJ MIA</t>
+  </si>
+  <si>
+    <t>A08140828</t>
+  </si>
+  <si>
+    <t>RASHEL AHMED</t>
+  </si>
+  <si>
+    <t>A20941515</t>
+  </si>
+  <si>
+    <t>MD SAKIBUL HASAN MILTON</t>
+  </si>
+  <si>
+    <t>A12054906</t>
+  </si>
+  <si>
+    <t>WALID MAHMUD</t>
+  </si>
+  <si>
+    <t>A09369386</t>
+  </si>
+  <si>
+    <t>MD SAIFUL ISLAM</t>
+  </si>
+  <si>
+    <t>A09804378</t>
+  </si>
+  <si>
+    <t>MD RAKIB HASSAN</t>
+  </si>
+  <si>
+    <t>A20555997</t>
+  </si>
+  <si>
+    <t>MD MOKTAR HOSSAIN</t>
+  </si>
+  <si>
+    <t>MST PARVIN AKTER</t>
+  </si>
+  <si>
+    <t>JAMAL KHAN</t>
+  </si>
+  <si>
+    <t>JIASMIN</t>
+  </si>
+  <si>
+    <t>MD MOYDAN ALI</t>
+  </si>
+  <si>
+    <t>MST NAZMA BEGUM</t>
+  </si>
+  <si>
+    <t>BACCHU MIAH</t>
+  </si>
+  <si>
+    <t>MST RENU BEGUM</t>
+  </si>
+  <si>
+    <t>TOFAZZAL</t>
+  </si>
+  <si>
+    <t>TASLIMA</t>
+  </si>
+  <si>
+    <t>MD LAL MIA</t>
+  </si>
+  <si>
+    <t>SAYERA KHATUN</t>
+  </si>
+  <si>
+    <t>REZAUL KARIM</t>
+  </si>
+  <si>
+    <t>KHOSHIDA BEGUM</t>
+  </si>
+  <si>
+    <t>MD MUNSUR ALI</t>
+  </si>
+  <si>
+    <t>MST RUMA KHATUN</t>
+  </si>
+  <si>
+    <t>MD ABU TAHER</t>
+  </si>
+  <si>
+    <t>MST SAIFUNNAHAR REKHA</t>
+  </si>
+  <si>
+    <t>MD SHAFIQUE ULLAH</t>
+  </si>
+  <si>
+    <t>RAHANA BEGUM</t>
+  </si>
+  <si>
+    <t>MD ALEK UDDIN</t>
+  </si>
+  <si>
+    <t>MAMATAZ BEGUM</t>
+  </si>
+  <si>
+    <t>Birth Date</t>
+  </si>
+  <si>
+    <t>Blood Group</t>
+  </si>
+  <si>
+    <t>Passport Issue Date</t>
+  </si>
+  <si>
+    <t>Passport Expire Date</t>
+  </si>
+  <si>
+    <t>Visa No</t>
+  </si>
+  <si>
+    <t>Visa Issue Date</t>
+  </si>
+  <si>
+    <t>Visa Expiry Date</t>
+  </si>
+  <si>
+    <t>Referral No</t>
+  </si>
+  <si>
+    <t>Employer</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>License No</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>BMET No</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>NID</t>
+  </si>
+  <si>
+    <t>Passport No 1</t>
+  </si>
+  <si>
+    <t>House/Vill/Road</t>
+  </si>
+  <si>
+    <t>Post Office</t>
+  </si>
+  <si>
+    <t>Police Station</t>
+  </si>
+  <si>
+    <t>Upazila</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>Division</t>
+  </si>
+  <si>
+    <t>Relation</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>O+</t>
+  </si>
+  <si>
+    <t>AB+</t>
+  </si>
+  <si>
+    <t>Serbia</t>
+  </si>
+  <si>
+    <t>A0935933</t>
+  </si>
+  <si>
+    <t>TANZANITE OVERSEAS</t>
+  </si>
+  <si>
+    <t>RL2124</t>
+  </si>
+  <si>
+    <t>01959216007</t>
+  </si>
+  <si>
+    <t>ABDUL KHALEK</t>
+  </si>
+  <si>
+    <t>BROTHER</t>
+  </si>
+  <si>
+    <t>SAGLAKANDI, SIRAJNAGOR, KERANIGANJ MODEL, KALATIYA - 1313, DHAKA</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>DHAKA</t>
+  </si>
+  <si>
+    <t>SHARIATPUR</t>
+  </si>
+  <si>
+    <t>JAMALPUR</t>
+  </si>
+  <si>
+    <t>HABIGANJ</t>
+  </si>
+  <si>
+    <t>CHUADANGA</t>
+  </si>
+  <si>
+    <t>CHATTOGRAM</t>
+  </si>
+  <si>
+    <t>MYMENSINGH</t>
+  </si>
+  <si>
+    <t>NARAYANGANJ</t>
+  </si>
+  <si>
+    <t>SYLHET</t>
+  </si>
+  <si>
+    <t>01981889066</t>
+  </si>
+  <si>
+    <t>01981889067</t>
+  </si>
+  <si>
+    <t>01981889068</t>
+  </si>
+  <si>
+    <t>01981889069</t>
+  </si>
+  <si>
+    <t>01981889070</t>
+  </si>
+  <si>
+    <t>01981889071</t>
+  </si>
+  <si>
+    <t>01981889072</t>
+  </si>
+  <si>
+    <t>01981889073</t>
+  </si>
+  <si>
+    <t>01981889074</t>
+  </si>
+  <si>
+    <t>01981889075</t>
+  </si>
+  <si>
+    <t>01981889076</t>
+  </si>
+  <si>
+    <t>KHULNA</t>
+  </si>
+  <si>
+    <t>ABDUL MALEK</t>
+  </si>
+  <si>
+    <t>RAHIM ALI</t>
+  </si>
+  <si>
+    <t>CINARCHAR, ISLAMPUR, ISLAMPUR - 2020, JAMALPUR</t>
+  </si>
+  <si>
+    <t>SONABIBI ROAD, BANDAR, BANDAR - 1410, NARAYANGANJ</t>
+  </si>
+  <si>
+    <t>NEW ALGIRCHAR, WARD NO-06, KERANIGANJ MODEL, ETAVARA - 1313, DHAKA</t>
+  </si>
+  <si>
+    <t>SHIBPUR, WORD NO-09, LAKHAI, MADNA - 3300, HABIGANJ</t>
+  </si>
+  <si>
+    <t>ALGIRCHAR, KERANIGANJ MODEL, ETAVARA - 1313, DHAKA</t>
+  </si>
+  <si>
+    <t>HATBOALIA, ALAMDANGA, HAT BOYALIA - 7210, CHUADANGA</t>
+  </si>
+  <si>
+    <t>KARIM ALIR BARI</t>
+  </si>
+  <si>
+    <t>SUJONPUR</t>
+  </si>
+  <si>
+    <t>KALIARGHAT</t>
+  </si>
+  <si>
+    <t>RAHIMGANJ</t>
+  </si>
+  <si>
+    <t>UTTARA WEST</t>
+  </si>
+  <si>
+    <t>AGROASIST DOO NOVI SAD</t>
+  </si>
+  <si>
+    <t>INTERSTAFF SERVICE DOO SOMBOR</t>
+  </si>
+  <si>
+    <t>A0935992</t>
+  </si>
+  <si>
+    <t>A0935945</t>
+  </si>
+  <si>
+    <t>A0935995</t>
+  </si>
+  <si>
+    <t>A0935916</t>
+  </si>
+  <si>
+    <t>A0935974</t>
+  </si>
+  <si>
+    <t>A0938116</t>
+  </si>
+  <si>
+    <t>A0938121</t>
+  </si>
+  <si>
+    <t>A0938118</t>
+  </si>
+  <si>
+    <t>A0938144</t>
+  </si>
+  <si>
+    <t>A0938133</t>
   </si>
 </sst>
 </file>
@@ -329,7 +607,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -517,18 +795,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF00FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA9999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD7E6B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -718,6 +1002,101 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -763,7 +1142,7 @@
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -771,20 +1150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -793,18 +1159,45 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="17" builtinId="30" customBuiltin="1"/>
@@ -1184,22 +1577,47 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21" style="19" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="38.28515625" style="19" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12" style="19" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14" style="19" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="29.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" style="19" customWidth="1"/>
+    <col min="27" max="27" width="8.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="29.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14" style="19" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="17.85546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="17.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14" style="19" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="85" style="19" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,331 +1642,1432 @@
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="X1" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y1" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA1" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB1" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC1" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD1" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE1" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF1" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG1" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH1" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI1" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ1" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK1" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM1" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN1" s="11" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="17">
-        <v>46077</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="13">
-        <v>20240037867</v>
+      <c r="D2" s="7">
+        <v>45062</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="22">
+        <v>20260037867</v>
       </c>
       <c r="H2" s="2">
         <v>6010533</v>
       </c>
-      <c r="I2" s="17">
-        <v>46142</v>
-      </c>
-      <c r="J2" s="10">
+      <c r="I2" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J2" s="5">
         <v>0.21528935185185186</v>
       </c>
+      <c r="K2" s="7">
+        <v>38224</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="M2" s="7">
+        <v>45062</v>
+      </c>
+      <c r="N2" s="7">
+        <v>48714</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" s="7">
+        <v>46224</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>46405</v>
+      </c>
+      <c r="S2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="T2" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U2" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V2" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="W2" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="X2" s="19">
+        <f>G2</f>
+        <v>20260037867</v>
+      </c>
+      <c r="Y2" s="19" t="str">
+        <f>B2</f>
+        <v>MAMUN HOSEN</v>
+      </c>
+      <c r="Z2" s="24">
+        <f>K2</f>
+        <v>38224</v>
+      </c>
+      <c r="AA2" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC2" s="19" t="str">
+        <f>Y2</f>
+        <v>MAMUN HOSEN</v>
+      </c>
+      <c r="AD2" s="19" t="str">
+        <f>C2</f>
+        <v>A07504029</v>
+      </c>
+      <c r="AE2" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF2" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG2" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH2" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI2" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ2" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK2" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL2" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM2" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="AN2" s="25" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3">
+    <row r="3" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="17">
-        <v>45280</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="13">
-        <v>20240037868</v>
+      <c r="D3" s="7">
+        <v>45008</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="22">
+        <v>20260037868</v>
       </c>
       <c r="H3" s="2">
         <v>6010536</v>
       </c>
-      <c r="I3" s="17">
-        <v>46143</v>
-      </c>
-      <c r="J3" s="10">
+      <c r="I3" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J3" s="5">
         <v>0.25695601851851901</v>
       </c>
+      <c r="K3" s="7">
+        <v>37188</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="M3" s="7">
+        <v>45008</v>
+      </c>
+      <c r="N3" s="7">
+        <v>48660</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="P3" s="7">
+        <v>46224</v>
+      </c>
+      <c r="Q3" s="7">
+        <v>46405</v>
+      </c>
+      <c r="S3" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="T3" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U3" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V3" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="W3" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="X3" s="19">
+        <f t="shared" ref="X3:X12" si="0">G3</f>
+        <v>20260037868</v>
+      </c>
+      <c r="Y3" s="19" t="str">
+        <f t="shared" ref="Y3:Y12" si="1">B3</f>
+        <v>RAYHAN KHAN</v>
+      </c>
+      <c r="Z3" s="24">
+        <f t="shared" ref="Z3:Z12" si="2">K3</f>
+        <v>37188</v>
+      </c>
+      <c r="AA3" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC3" s="19" t="str">
+        <f t="shared" ref="AC3:AC12" si="3">Y3</f>
+        <v>RAYHAN KHAN</v>
+      </c>
+      <c r="AD3" s="19" t="str">
+        <f t="shared" ref="AD3:AD12" si="4">C3</f>
+        <v>A07322494</v>
+      </c>
+      <c r="AE3" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF3" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG3" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH3" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI3" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ3" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK3" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL3" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM3" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="AN3" s="12" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="17">
-        <v>45956</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="13">
-        <v>20240037869</v>
+      <c r="D4" s="7">
+        <v>44600</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="22">
+        <v>20260037869</v>
       </c>
       <c r="H4" s="2">
         <v>6010539</v>
       </c>
-      <c r="I4" s="17">
-        <v>46144</v>
-      </c>
-      <c r="J4" s="10">
+      <c r="I4" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J4" s="5">
         <v>0.29862268518518498</v>
       </c>
+      <c r="K4" s="7">
+        <v>36121</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="M4" s="7">
+        <v>44600</v>
+      </c>
+      <c r="N4" s="7">
+        <v>48251</v>
+      </c>
+      <c r="O4" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="P4" s="7">
+        <v>46224</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>46405</v>
+      </c>
+      <c r="S4" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="T4" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U4" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V4" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="W4" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="X4" s="19">
+        <f t="shared" si="0"/>
+        <v>20260037869</v>
+      </c>
+      <c r="Y4" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MD NAJIM UDDIN</v>
+      </c>
+      <c r="Z4" s="24">
+        <f t="shared" si="2"/>
+        <v>36121</v>
+      </c>
+      <c r="AA4" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC4" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>MD NAJIM UDDIN</v>
+      </c>
+      <c r="AD4" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>A03131255</v>
+      </c>
+      <c r="AE4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF4" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG4" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="AH4" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="AI4" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="AJ4" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK4" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL4" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM4" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="AN4" s="13" t="s">
+        <v>117</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5">
+    <row r="5" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="17">
-        <v>44916</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="13">
-        <v>20240037870</v>
+      <c r="D5" s="7">
+        <v>45606</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="22">
+        <v>20260037870</v>
       </c>
       <c r="H5" s="2">
         <v>6010542</v>
       </c>
-      <c r="I5" s="17">
-        <v>46145</v>
-      </c>
-      <c r="J5" s="10">
+      <c r="I5" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J5" s="5">
         <v>0.340289351851852</v>
       </c>
+      <c r="K5" s="7">
+        <v>36382</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="M5" s="7">
+        <v>45606</v>
+      </c>
+      <c r="N5" s="7">
+        <v>49257</v>
+      </c>
+      <c r="O5" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="P5" s="7">
+        <v>46224</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>46405</v>
+      </c>
+      <c r="S5" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="T5" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U5" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V5" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="W5" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="X5" s="19">
+        <f t="shared" si="0"/>
+        <v>20260037870</v>
+      </c>
+      <c r="Y5" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>RAKIBUL HASAN</v>
+      </c>
+      <c r="Z5" s="24">
+        <f t="shared" si="2"/>
+        <v>36382</v>
+      </c>
+      <c r="AA5" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC5" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>RAKIBUL HASAN</v>
+      </c>
+      <c r="AD5" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>A16817519</v>
+      </c>
+      <c r="AE5" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF5" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG5" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH5" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI5" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AJ5" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK5" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL5" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM5" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN5" s="13" t="s">
+        <v>118</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="17">
-        <v>45571</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="13">
-        <v>20240037871</v>
+      <c r="D6" s="7">
+        <v>44636</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="22">
+        <v>20260037871</v>
       </c>
       <c r="H6" s="2">
         <v>6010545</v>
       </c>
-      <c r="I6" s="17">
-        <v>46146</v>
-      </c>
-      <c r="J6" s="10">
+      <c r="I6" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J6" s="5">
         <v>0.38195601851851901</v>
       </c>
+      <c r="K6" s="7">
+        <v>36741</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="M6" s="7">
+        <v>44636</v>
+      </c>
+      <c r="N6" s="7">
+        <v>48288</v>
+      </c>
+      <c r="O6" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="P6" s="7">
+        <v>46224</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>46405</v>
+      </c>
+      <c r="S6" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="T6" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U6" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V6" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="X6" s="19">
+        <f t="shared" si="0"/>
+        <v>20260037871</v>
+      </c>
+      <c r="Y6" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>SUMON AHMED</v>
+      </c>
+      <c r="Z6" s="24">
+        <f t="shared" si="2"/>
+        <v>36741</v>
+      </c>
+      <c r="AA6" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC6" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>SUMON AHMED</v>
+      </c>
+      <c r="AD6" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>A03349685</v>
+      </c>
+      <c r="AE6" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF6" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG6" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK6" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL6" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM6" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="AN6" s="12" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7">
+    <row r="7" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="17">
-        <v>45118</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="13">
-        <v>20240037872</v>
+      <c r="D7" s="7">
+        <v>45077</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="22">
+        <v>20260037872</v>
       </c>
       <c r="H7" s="2">
         <v>6010548</v>
       </c>
-      <c r="I7" s="17">
-        <v>46147</v>
-      </c>
-      <c r="J7" s="10">
+      <c r="I7" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J7" s="5">
         <v>0.42362268518518498</v>
       </c>
+      <c r="K7" s="7">
+        <v>34720</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="M7" s="7">
+        <v>45077</v>
+      </c>
+      <c r="N7" s="7">
+        <v>48729</v>
+      </c>
+      <c r="O7" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="P7" s="7">
+        <v>46224</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>46405</v>
+      </c>
+      <c r="S7" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U7" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V7" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="W7" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="X7" s="19">
+        <f t="shared" si="0"/>
+        <v>20260037872</v>
+      </c>
+      <c r="Y7" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MD SABUJ MIA</v>
+      </c>
+      <c r="Z7" s="24">
+        <f t="shared" si="2"/>
+        <v>34720</v>
+      </c>
+      <c r="AA7" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC7" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>MD SABUJ MIA</v>
+      </c>
+      <c r="AD7" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>A08140828</v>
+      </c>
+      <c r="AE7" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF7" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG7" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH7" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="AI7" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="AJ7" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK7" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL7" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM7" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN7" s="13" t="s">
+        <v>117</v>
+      </c>
     </row>
-    <row r="8" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="17">
-        <v>44921</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="13">
-        <v>20240037873</v>
+      <c r="D8" s="7">
+        <v>45984</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="22">
+        <v>20260037873</v>
       </c>
       <c r="H8" s="2">
         <v>6010551</v>
       </c>
-      <c r="I8" s="17">
-        <v>46148</v>
-      </c>
-      <c r="J8" s="10">
+      <c r="I8" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J8" s="5">
         <v>0.465289351851852</v>
       </c>
+      <c r="K8" s="7">
+        <v>36629</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="M8" s="7">
+        <v>45984</v>
+      </c>
+      <c r="N8" s="7">
+        <v>49635</v>
+      </c>
+      <c r="O8" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="P8" s="7">
+        <v>46239</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>46424</v>
+      </c>
+      <c r="S8" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="T8" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U8" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V8" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="W8" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="X8" s="19">
+        <f t="shared" si="0"/>
+        <v>20260037873</v>
+      </c>
+      <c r="Y8" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>RASHEL AHMED</v>
+      </c>
+      <c r="Z8" s="24">
+        <f t="shared" si="2"/>
+        <v>36629</v>
+      </c>
+      <c r="AA8" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC8" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>RASHEL AHMED</v>
+      </c>
+      <c r="AD8" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>A20941515</v>
+      </c>
+      <c r="AE8" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF8" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG8" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH8" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI8" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ8" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK8" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL8" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM8" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN8" s="13" t="s">
+        <v>118</v>
+      </c>
     </row>
-    <row r="9" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="9" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="17">
-        <v>46049</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="13">
-        <v>20240037874</v>
+      <c r="D9" s="7">
+        <v>45200</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="22">
+        <v>20260037874</v>
       </c>
       <c r="H9" s="2">
         <v>6010554</v>
       </c>
-      <c r="I9" s="17">
-        <v>46149</v>
-      </c>
-      <c r="J9" s="10">
+      <c r="I9" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J9" s="5">
         <v>0.50695601851851901</v>
       </c>
+      <c r="K9" s="7">
+        <v>38420</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="M9" s="7">
+        <v>45200</v>
+      </c>
+      <c r="N9" s="7">
+        <v>48852</v>
+      </c>
+      <c r="O9" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="P9" s="7">
+        <v>46239</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>46424</v>
+      </c>
+      <c r="S9" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="T9" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U9" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V9" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="X9" s="19">
+        <f t="shared" si="0"/>
+        <v>20260037874</v>
+      </c>
+      <c r="Y9" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MD SAKIBUL HASAN MILTON</v>
+      </c>
+      <c r="Z9" s="24">
+        <f t="shared" si="2"/>
+        <v>38420</v>
+      </c>
+      <c r="AA9" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC9" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>MD SAKIBUL HASAN MILTON</v>
+      </c>
+      <c r="AD9" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>A12054906</v>
+      </c>
+      <c r="AE9" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF9" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG9" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH9" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI9" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ9" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK9" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL9" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM9" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="AN9" s="13" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="10" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="17">
-        <v>44231</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="13">
-        <v>20240037875</v>
+      <c r="D10" s="7">
+        <v>45834</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="22">
+        <v>20260037875</v>
       </c>
       <c r="H10" s="2">
         <v>6010557</v>
       </c>
-      <c r="I10" s="17">
-        <v>46150</v>
-      </c>
-      <c r="J10" s="10">
+      <c r="I10" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J10" s="5">
         <v>0.54862268518518498</v>
       </c>
+      <c r="K10" s="7">
+        <v>38158</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="7">
+        <v>45834</v>
+      </c>
+      <c r="N10" s="7">
+        <v>49485</v>
+      </c>
+      <c r="O10" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="P10" s="7">
+        <v>46239</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>46424</v>
+      </c>
+      <c r="S10" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="T10" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U10" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V10" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="W10" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="X10" s="19">
+        <f t="shared" si="0"/>
+        <v>20260037875</v>
+      </c>
+      <c r="Y10" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>WALID MAHMUD</v>
+      </c>
+      <c r="Z10" s="24">
+        <f t="shared" si="2"/>
+        <v>38158</v>
+      </c>
+      <c r="AA10" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC10" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>WALID MAHMUD</v>
+      </c>
+      <c r="AD10" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>A09369386</v>
+      </c>
+      <c r="AE10" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF10" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG10" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH10" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI10" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ10" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK10" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="AL10" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM10" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN10" s="14" t="s">
+        <v>120</v>
+      </c>
     </row>
-    <row r="11" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11">
+    <row r="11" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="17">
-        <v>45886</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="13">
-        <v>20240037876</v>
+      <c r="D11" s="7">
+        <v>46042</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="22">
+        <v>20260037876</v>
       </c>
       <c r="H11" s="2">
         <v>6010560</v>
       </c>
-      <c r="I11" s="17">
-        <v>46151</v>
-      </c>
-      <c r="J11" s="10">
+      <c r="I11" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J11" s="5">
         <v>0.59028935185185205</v>
+      </c>
+      <c r="K11" s="7">
+        <v>35860</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="M11" s="7">
+        <v>46042</v>
+      </c>
+      <c r="N11" s="7">
+        <v>49693</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="P11" s="7">
+        <v>46239</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>46424</v>
+      </c>
+      <c r="S11" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="T11" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U11" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V11" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="W11" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="X11" s="19">
+        <f t="shared" si="0"/>
+        <v>20260037876</v>
+      </c>
+      <c r="Y11" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MD SAIFUL ISLAM</v>
+      </c>
+      <c r="Z11" s="24">
+        <f t="shared" si="2"/>
+        <v>35860</v>
+      </c>
+      <c r="AA11" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC11" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>MD SAIFUL ISLAM</v>
+      </c>
+      <c r="AD11" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>A09804378</v>
+      </c>
+      <c r="AE11" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF11" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG11" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH11" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI11" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ11" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK11" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AL11" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM11" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="AN11" s="15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="7">
+        <v>45947</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="22">
+        <v>20260037877</v>
+      </c>
+      <c r="H12" s="2">
+        <v>6010563</v>
+      </c>
+      <c r="I12" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0.63195601851851901</v>
+      </c>
+      <c r="K12" s="7">
+        <v>39248</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="M12" s="7">
+        <v>45947</v>
+      </c>
+      <c r="N12" s="7">
+        <v>49598</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="P12" s="7">
+        <v>46239</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>46424</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="W12" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="X12" s="19">
+        <f t="shared" si="0"/>
+        <v>20260037877</v>
+      </c>
+      <c r="Y12" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>MD RAKIB HASSAN</v>
+      </c>
+      <c r="Z12" s="24">
+        <f t="shared" si="2"/>
+        <v>39248</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC12" s="19" t="str">
+        <f t="shared" si="3"/>
+        <v>MD RAKIB HASSAN</v>
+      </c>
+      <c r="AD12" s="19" t="str">
+        <f t="shared" si="4"/>
+        <v>A20555997</v>
+      </c>
+      <c r="AE12" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF12" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG12" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="AH12" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AI12" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AJ12" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="AM12" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="AN12" s="25" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BED1F8-692F-407A-94A8-F558374C2374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1D1657-5055-49EE-BC45-7B07A088E75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="127">
   <si>
     <t>SL NO</t>
   </si>
@@ -294,9 +294,6 @@
     <t>RL2124</t>
   </si>
   <si>
-    <t>01959216007</t>
-  </si>
-  <si>
     <t>ABDUL KHALEK</t>
   </si>
   <si>
@@ -334,39 +331,6 @@
   </si>
   <si>
     <t>SYLHET</t>
-  </si>
-  <si>
-    <t>01981889066</t>
-  </si>
-  <si>
-    <t>01981889067</t>
-  </si>
-  <si>
-    <t>01981889068</t>
-  </si>
-  <si>
-    <t>01981889069</t>
-  </si>
-  <si>
-    <t>01981889070</t>
-  </si>
-  <si>
-    <t>01981889071</t>
-  </si>
-  <si>
-    <t>01981889072</t>
-  </si>
-  <si>
-    <t>01981889073</t>
-  </si>
-  <si>
-    <t>01981889074</t>
-  </si>
-  <si>
-    <t>01981889075</t>
-  </si>
-  <si>
-    <t>01981889076</t>
   </si>
   <si>
     <t>KHULNA</t>
@@ -1142,7 +1106,7 @@
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1177,27 +1141,25 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="17" builtinId="30" customBuiltin="1"/>
@@ -1580,41 +1542,40 @@
   <dimension ref="A1:AN12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.5703125" style="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21" style="19" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="38.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12" style="19" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14" style="19" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="29.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.140625" style="19" customWidth="1"/>
-    <col min="27" max="27" width="8.5703125" style="19" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.5703125" style="19" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="29.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14" style="19" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="17.85546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="17.140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14" style="19" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="85" style="19" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="19"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" customWidth="1"/>
+    <col min="27" max="27" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="85" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1746,7 +1707,7 @@
       <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="7">
@@ -1755,10 +1716,10 @@
       <c r="E2" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="21">
         <v>20260037867</v>
       </c>
       <c r="H2" s="2">
@@ -1773,7 +1734,7 @@
       <c r="K2" s="7">
         <v>38224</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" t="s">
         <v>80</v>
       </c>
       <c r="M2" s="7">
@@ -1782,7 +1743,7 @@
       <c r="N2" s="7">
         <v>48714</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" t="s">
         <v>85</v>
       </c>
       <c r="P2" s="7">
@@ -1791,77 +1752,77 @@
       <c r="Q2" s="7">
         <v>46405</v>
       </c>
-      <c r="S2" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="T2" s="19" t="s">
+      <c r="S2" t="s">
+        <v>116</v>
+      </c>
+      <c r="T2" t="s">
         <v>84</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="U2" t="s">
         <v>86</v>
       </c>
-      <c r="V2" s="19" t="s">
+      <c r="V2" t="s">
         <v>87</v>
       </c>
-      <c r="W2" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="X2" s="19">
+      <c r="W2" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X2">
         <f>G2</f>
         <v>20260037867</v>
       </c>
-      <c r="Y2" s="19" t="str">
+      <c r="Y2" t="str">
         <f>B2</f>
         <v>MAMUN HOSEN</v>
       </c>
-      <c r="Z2" s="24">
+      <c r="Z2" s="22">
         <f>K2</f>
         <v>38224</v>
       </c>
-      <c r="AA2" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC2" s="19" t="str">
+      <c r="AA2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC2" t="str">
         <f>Y2</f>
         <v>MAMUN HOSEN</v>
       </c>
-      <c r="AD2" s="19" t="str">
+      <c r="AD2" t="str">
         <f>C2</f>
         <v>A07504029</v>
       </c>
-      <c r="AE2" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF2" s="19" t="s">
-        <v>122</v>
+      <c r="AE2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>110</v>
       </c>
       <c r="AG2" s="12" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="AH2" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI2" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ2" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK2" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL2" t="s">
         <v>89</v>
       </c>
-      <c r="AL2" s="19" t="s">
+      <c r="AM2" s="30">
+        <v>8801959215972</v>
+      </c>
+      <c r="AN2" s="23" t="s">
         <v>90</v>
-      </c>
-      <c r="AM2" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="AN2" s="25" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="19">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1876,10 +1837,10 @@
       <c r="E3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="21">
         <v>20260037868</v>
       </c>
       <c r="H3" s="2">
@@ -1894,7 +1855,7 @@
       <c r="K3" s="7">
         <v>37188</v>
       </c>
-      <c r="L3" s="19" t="s">
+      <c r="L3" t="s">
         <v>81</v>
       </c>
       <c r="M3" s="7">
@@ -1903,8 +1864,8 @@
       <c r="N3" s="7">
         <v>48660</v>
       </c>
-      <c r="O3" s="19" t="s">
-        <v>129</v>
+      <c r="O3" t="s">
+        <v>117</v>
       </c>
       <c r="P3" s="7">
         <v>46224</v>
@@ -1912,73 +1873,73 @@
       <c r="Q3" s="7">
         <v>46405</v>
       </c>
-      <c r="S3" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="T3" s="19" t="s">
+      <c r="S3" t="s">
+        <v>116</v>
+      </c>
+      <c r="T3" t="s">
         <v>84</v>
       </c>
-      <c r="U3" s="19" t="s">
+      <c r="U3" t="s">
         <v>86</v>
       </c>
-      <c r="V3" s="19" t="s">
+      <c r="V3" t="s">
         <v>87</v>
       </c>
-      <c r="W3" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="X3" s="19">
+      <c r="W3" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X3">
         <f t="shared" ref="X3:X12" si="0">G3</f>
         <v>20260037868</v>
       </c>
-      <c r="Y3" s="19" t="str">
+      <c r="Y3" t="str">
         <f t="shared" ref="Y3:Y12" si="1">B3</f>
         <v>RAYHAN KHAN</v>
       </c>
-      <c r="Z3" s="24">
+      <c r="Z3" s="22">
         <f t="shared" ref="Z3:Z12" si="2">K3</f>
         <v>37188</v>
       </c>
-      <c r="AA3" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC3" s="19" t="str">
+      <c r="AA3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC3" t="str">
         <f t="shared" ref="AC3:AC12" si="3">Y3</f>
         <v>RAYHAN KHAN</v>
       </c>
-      <c r="AD3" s="19" t="str">
+      <c r="AD3" t="str">
         <f t="shared" ref="AD3:AD12" si="4">C3</f>
         <v>A07322494</v>
       </c>
-      <c r="AE3" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF3" s="19" t="s">
-        <v>123</v>
+      <c r="AE3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>111</v>
       </c>
       <c r="AG3" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH3" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI3" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AJ3" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK3" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="AL3" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM3" s="23" t="s">
-        <v>103</v>
+        <v>92</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM3" s="30">
+        <v>8801959215977</v>
       </c>
       <c r="AN3" s="12" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1988,7 +1949,7 @@
       <c r="B4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="7">
@@ -1997,10 +1958,10 @@
       <c r="E4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="21">
         <v>20260037869</v>
       </c>
       <c r="H4" s="2">
@@ -2015,7 +1976,7 @@
       <c r="K4" s="7">
         <v>36121</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" t="s">
         <v>80</v>
       </c>
       <c r="M4" s="7">
@@ -2024,8 +1985,8 @@
       <c r="N4" s="7">
         <v>48251</v>
       </c>
-      <c r="O4" s="19" t="s">
-        <v>130</v>
+      <c r="O4" t="s">
+        <v>118</v>
       </c>
       <c r="P4" s="7">
         <v>46224</v>
@@ -2033,83 +1994,83 @@
       <c r="Q4" s="7">
         <v>46405</v>
       </c>
-      <c r="S4" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="T4" s="19" t="s">
+      <c r="S4" t="s">
+        <v>116</v>
+      </c>
+      <c r="T4" t="s">
         <v>84</v>
       </c>
-      <c r="U4" s="19" t="s">
+      <c r="U4" t="s">
         <v>86</v>
       </c>
-      <c r="V4" s="19" t="s">
+      <c r="V4" t="s">
         <v>87</v>
       </c>
-      <c r="W4" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="X4" s="19">
+      <c r="W4" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X4">
         <f t="shared" si="0"/>
         <v>20260037869</v>
       </c>
-      <c r="Y4" s="19" t="str">
+      <c r="Y4" t="str">
         <f t="shared" si="1"/>
         <v>MD NAJIM UDDIN</v>
       </c>
-      <c r="Z4" s="24">
+      <c r="Z4" s="22">
         <f t="shared" si="2"/>
         <v>36121</v>
       </c>
-      <c r="AA4" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC4" s="19" t="str">
+      <c r="AA4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC4" t="str">
         <f t="shared" si="3"/>
         <v>MD NAJIM UDDIN</v>
       </c>
-      <c r="AD4" s="19" t="str">
+      <c r="AD4" t="str">
         <f t="shared" si="4"/>
         <v>A03131255</v>
       </c>
-      <c r="AE4" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF4" s="19" t="s">
-        <v>124</v>
+      <c r="AE4" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>112</v>
       </c>
       <c r="AG4" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AH4" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AI4" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="AJ4" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK4" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="AL4" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM4" s="23" t="s">
-        <v>104</v>
+        <v>94</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM4" s="30">
+        <v>8801959215982</v>
       </c>
       <c r="AN4" s="13" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="25" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="7">
@@ -2118,10 +2079,10 @@
       <c r="E5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="21">
         <v>20260037870</v>
       </c>
       <c r="H5" s="2">
@@ -2136,7 +2097,7 @@
       <c r="K5" s="7">
         <v>36382</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" t="s">
         <v>82</v>
       </c>
       <c r="M5" s="7">
@@ -2145,8 +2106,8 @@
       <c r="N5" s="7">
         <v>49257</v>
       </c>
-      <c r="O5" s="19" t="s">
-        <v>131</v>
+      <c r="O5" t="s">
+        <v>119</v>
       </c>
       <c r="P5" s="7">
         <v>46224</v>
@@ -2154,73 +2115,73 @@
       <c r="Q5" s="7">
         <v>46405</v>
       </c>
-      <c r="S5" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="T5" s="19" t="s">
+      <c r="S5" t="s">
+        <v>116</v>
+      </c>
+      <c r="T5" t="s">
         <v>84</v>
       </c>
-      <c r="U5" s="19" t="s">
+      <c r="U5" t="s">
         <v>86</v>
       </c>
-      <c r="V5" s="19" t="s">
+      <c r="V5" t="s">
         <v>87</v>
       </c>
-      <c r="W5" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="X5" s="19">
+      <c r="W5" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X5">
         <f t="shared" si="0"/>
         <v>20260037870</v>
       </c>
-      <c r="Y5" s="19" t="str">
+      <c r="Y5" t="str">
         <f t="shared" si="1"/>
         <v>RAKIBUL HASAN</v>
       </c>
-      <c r="Z5" s="24">
+      <c r="Z5" s="22">
         <f t="shared" si="2"/>
         <v>36382</v>
       </c>
-      <c r="AA5" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC5" s="19" t="str">
+      <c r="AA5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC5" t="str">
         <f t="shared" si="3"/>
         <v>RAKIBUL HASAN</v>
       </c>
-      <c r="AD5" s="19" t="str">
+      <c r="AD5" t="str">
         <f t="shared" si="4"/>
         <v>A16817519</v>
       </c>
-      <c r="AE5" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF5" s="32" t="s">
-        <v>125</v>
+      <c r="AE5" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>113</v>
       </c>
       <c r="AG5" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH5" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AI5" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AJ5" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK5" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL5" t="s">
         <v>89</v>
       </c>
-      <c r="AL5" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM5" s="23" t="s">
-        <v>105</v>
+      <c r="AM5" s="30">
+        <v>8801959215987</v>
       </c>
       <c r="AN5" s="13" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2230,7 +2191,7 @@
       <c r="B6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="25" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="7">
@@ -2239,10 +2200,10 @@
       <c r="E6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="21">
         <v>20260037871</v>
       </c>
       <c r="H6" s="2">
@@ -2257,7 +2218,7 @@
       <c r="K6" s="7">
         <v>36741</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" t="s">
         <v>83</v>
       </c>
       <c r="M6" s="7">
@@ -2266,8 +2227,8 @@
       <c r="N6" s="7">
         <v>48288</v>
       </c>
-      <c r="O6" s="19" t="s">
-        <v>132</v>
+      <c r="O6" t="s">
+        <v>120</v>
       </c>
       <c r="P6" s="7">
         <v>46224</v>
@@ -2275,83 +2236,83 @@
       <c r="Q6" s="7">
         <v>46405</v>
       </c>
-      <c r="S6" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="T6" s="19" t="s">
+      <c r="S6" t="s">
+        <v>116</v>
+      </c>
+      <c r="T6" t="s">
         <v>84</v>
       </c>
-      <c r="U6" s="19" t="s">
+      <c r="U6" t="s">
         <v>86</v>
       </c>
-      <c r="V6" s="19" t="s">
+      <c r="V6" t="s">
         <v>87</v>
       </c>
-      <c r="W6" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="X6" s="19">
+      <c r="W6" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X6">
         <f t="shared" si="0"/>
         <v>20260037871</v>
       </c>
-      <c r="Y6" s="19" t="str">
+      <c r="Y6" t="str">
         <f t="shared" si="1"/>
         <v>SUMON AHMED</v>
       </c>
-      <c r="Z6" s="24">
+      <c r="Z6" s="22">
         <f t="shared" si="2"/>
         <v>36741</v>
       </c>
-      <c r="AA6" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC6" s="19" t="str">
+      <c r="AA6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC6" t="str">
         <f t="shared" si="3"/>
         <v>SUMON AHMED</v>
       </c>
-      <c r="AD6" s="19" t="str">
+      <c r="AD6" t="str">
         <f t="shared" si="4"/>
         <v>A03349685</v>
       </c>
-      <c r="AE6" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF6" s="19" t="s">
-        <v>122</v>
+      <c r="AE6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>110</v>
       </c>
       <c r="AG6" s="12" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="AH6" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI6" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ6" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK6" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="AL6" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM6" s="23" t="s">
-        <v>106</v>
+        <v>92</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM6" s="30">
+        <v>8801959215992</v>
       </c>
       <c r="AN6" s="12" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19">
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="25" t="s">
         <v>21</v>
       </c>
       <c r="D7" s="7">
@@ -2360,10 +2321,10 @@
       <c r="E7" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="21">
         <v>20260037872</v>
       </c>
       <c r="H7" s="2">
@@ -2378,7 +2339,7 @@
       <c r="K7" s="7">
         <v>34720</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" t="s">
         <v>80</v>
       </c>
       <c r="M7" s="7">
@@ -2387,8 +2348,8 @@
       <c r="N7" s="7">
         <v>48729</v>
       </c>
-      <c r="O7" s="19" t="s">
-        <v>133</v>
+      <c r="O7" t="s">
+        <v>121</v>
       </c>
       <c r="P7" s="7">
         <v>46224</v>
@@ -2396,73 +2357,73 @@
       <c r="Q7" s="7">
         <v>46405</v>
       </c>
-      <c r="S7" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="T7" s="19" t="s">
+      <c r="S7" t="s">
+        <v>116</v>
+      </c>
+      <c r="T7" t="s">
         <v>84</v>
       </c>
-      <c r="U7" s="19" t="s">
+      <c r="U7" t="s">
         <v>86</v>
       </c>
-      <c r="V7" s="19" t="s">
+      <c r="V7" t="s">
         <v>87</v>
       </c>
-      <c r="W7" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="X7" s="19">
+      <c r="W7" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X7">
         <f t="shared" si="0"/>
         <v>20260037872</v>
       </c>
-      <c r="Y7" s="19" t="str">
+      <c r="Y7" t="str">
         <f t="shared" si="1"/>
         <v>MD SABUJ MIA</v>
       </c>
-      <c r="Z7" s="24">
+      <c r="Z7" s="22">
         <f t="shared" si="2"/>
         <v>34720</v>
       </c>
-      <c r="AA7" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC7" s="19" t="str">
+      <c r="AA7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC7" t="str">
         <f t="shared" si="3"/>
         <v>MD SABUJ MIA</v>
       </c>
-      <c r="AD7" s="19" t="str">
+      <c r="AD7" t="str">
         <f t="shared" si="4"/>
         <v>A08140828</v>
       </c>
-      <c r="AE7" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF7" s="19" t="s">
-        <v>123</v>
+      <c r="AE7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>111</v>
       </c>
       <c r="AG7" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AH7" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AI7" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AJ7" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK7" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="AL7" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM7" s="23" t="s">
-        <v>107</v>
+        <v>100</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM7" s="30">
+        <v>8801959215997</v>
       </c>
       <c r="AN7" s="13" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2472,19 +2433,19 @@
       <c r="B8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="25" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="7">
         <v>45984</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="21">
         <v>20260037873</v>
       </c>
       <c r="H8" s="2">
@@ -2499,7 +2460,7 @@
       <c r="K8" s="7">
         <v>36629</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" t="s">
         <v>80</v>
       </c>
       <c r="M8" s="7">
@@ -2508,8 +2469,8 @@
       <c r="N8" s="7">
         <v>49635</v>
       </c>
-      <c r="O8" s="19" t="s">
-        <v>134</v>
+      <c r="O8" t="s">
+        <v>122</v>
       </c>
       <c r="P8" s="7">
         <v>46239</v>
@@ -2517,83 +2478,83 @@
       <c r="Q8" s="7">
         <v>46424</v>
       </c>
-      <c r="S8" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="T8" s="19" t="s">
+      <c r="S8" t="s">
+        <v>115</v>
+      </c>
+      <c r="T8" t="s">
         <v>84</v>
       </c>
-      <c r="U8" s="19" t="s">
+      <c r="U8" t="s">
         <v>86</v>
       </c>
-      <c r="V8" s="19" t="s">
+      <c r="V8" t="s">
         <v>87</v>
       </c>
-      <c r="W8" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="X8" s="19">
+      <c r="W8" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X8">
         <f t="shared" si="0"/>
         <v>20260037873</v>
       </c>
-      <c r="Y8" s="19" t="str">
+      <c r="Y8" t="str">
         <f t="shared" si="1"/>
         <v>RASHEL AHMED</v>
       </c>
-      <c r="Z8" s="24">
+      <c r="Z8" s="22">
         <f t="shared" si="2"/>
         <v>36629</v>
       </c>
-      <c r="AA8" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC8" s="19" t="str">
+      <c r="AA8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC8" t="str">
         <f t="shared" si="3"/>
         <v>RASHEL AHMED</v>
       </c>
-      <c r="AD8" s="19" t="str">
+      <c r="AD8" t="str">
         <f t="shared" si="4"/>
         <v>A20941515</v>
       </c>
-      <c r="AE8" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF8" s="19" t="s">
-        <v>124</v>
+      <c r="AE8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>112</v>
       </c>
       <c r="AG8" s="12" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="AH8" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI8" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ8" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK8" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL8" t="s">
         <v>89</v>
       </c>
-      <c r="AL8" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM8" s="23" t="s">
-        <v>108</v>
+      <c r="AM8" s="30">
+        <v>8801959216002</v>
       </c>
       <c r="AN8" s="13" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19">
+      <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="25" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="7">
@@ -2605,7 +2566,7 @@
       <c r="F9" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="21">
         <v>20260037874</v>
       </c>
       <c r="H9" s="2">
@@ -2620,7 +2581,7 @@
       <c r="K9" s="7">
         <v>38420</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="L9" t="s">
         <v>80</v>
       </c>
       <c r="M9" s="7">
@@ -2629,8 +2590,8 @@
       <c r="N9" s="7">
         <v>48852</v>
       </c>
-      <c r="O9" s="19" t="s">
-        <v>135</v>
+      <c r="O9" t="s">
+        <v>123</v>
       </c>
       <c r="P9" s="7">
         <v>46239</v>
@@ -2638,73 +2599,73 @@
       <c r="Q9" s="7">
         <v>46424</v>
       </c>
-      <c r="S9" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="T9" s="19" t="s">
+      <c r="S9" t="s">
+        <v>115</v>
+      </c>
+      <c r="T9" t="s">
         <v>84</v>
       </c>
-      <c r="U9" s="19" t="s">
+      <c r="U9" t="s">
         <v>86</v>
       </c>
-      <c r="V9" s="19" t="s">
+      <c r="V9" t="s">
         <v>87</v>
       </c>
-      <c r="W9" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="X9" s="19">
+      <c r="W9" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X9">
         <f t="shared" si="0"/>
         <v>20260037874</v>
       </c>
-      <c r="Y9" s="19" t="str">
+      <c r="Y9" t="str">
         <f t="shared" si="1"/>
         <v>MD SAKIBUL HASAN MILTON</v>
       </c>
-      <c r="Z9" s="24">
+      <c r="Z9" s="22">
         <f t="shared" si="2"/>
         <v>38420</v>
       </c>
-      <c r="AA9" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC9" s="19" t="str">
+      <c r="AA9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC9" t="str">
         <f t="shared" si="3"/>
         <v>MD SAKIBUL HASAN MILTON</v>
       </c>
-      <c r="AD9" s="19" t="str">
+      <c r="AD9" t="str">
         <f t="shared" si="4"/>
         <v>A12054906</v>
       </c>
-      <c r="AE9" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF9" s="19" t="s">
-        <v>122</v>
+      <c r="AE9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>110</v>
       </c>
       <c r="AG9" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH9" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AI9" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ9" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="AK9" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="AL9" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM9" s="23" t="s">
-        <v>109</v>
+        <v>101</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM9" s="30">
+        <v>8801959216007</v>
       </c>
       <c r="AN9" s="13" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -2714,19 +2675,19 @@
       <c r="B10" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="25" t="s">
         <v>27</v>
       </c>
       <c r="D10" s="7">
         <v>45834</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="21">
         <v>20260037875</v>
       </c>
       <c r="H10" s="2">
@@ -2741,7 +2702,7 @@
       <c r="K10" s="7">
         <v>38158</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" t="s">
         <v>82</v>
       </c>
       <c r="M10" s="7">
@@ -2750,8 +2711,8 @@
       <c r="N10" s="7">
         <v>49485</v>
       </c>
-      <c r="O10" s="19" t="s">
-        <v>137</v>
+      <c r="O10" t="s">
+        <v>125</v>
       </c>
       <c r="P10" s="7">
         <v>46239</v>
@@ -2759,83 +2720,83 @@
       <c r="Q10" s="7">
         <v>46424</v>
       </c>
-      <c r="S10" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="T10" s="19" t="s">
+      <c r="S10" t="s">
+        <v>115</v>
+      </c>
+      <c r="T10" t="s">
         <v>84</v>
       </c>
-      <c r="U10" s="19" t="s">
+      <c r="U10" t="s">
         <v>86</v>
       </c>
-      <c r="V10" s="19" t="s">
+      <c r="V10" t="s">
         <v>87</v>
       </c>
-      <c r="W10" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="X10" s="19">
+      <c r="W10" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X10">
         <f t="shared" si="0"/>
         <v>20260037875</v>
       </c>
-      <c r="Y10" s="19" t="str">
+      <c r="Y10" t="str">
         <f t="shared" si="1"/>
         <v>WALID MAHMUD</v>
       </c>
-      <c r="Z10" s="24">
+      <c r="Z10" s="22">
         <f t="shared" si="2"/>
         <v>38158</v>
       </c>
-      <c r="AA10" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC10" s="19" t="str">
+      <c r="AA10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC10" t="str">
         <f t="shared" si="3"/>
         <v>WALID MAHMUD</v>
       </c>
-      <c r="AD10" s="19" t="str">
+      <c r="AD10" t="str">
         <f t="shared" si="4"/>
         <v>A09369386</v>
       </c>
-      <c r="AE10" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="AF10" s="19" t="s">
-        <v>123</v>
+      <c r="AE10" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>111</v>
       </c>
       <c r="AG10" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH10" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AI10" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ10" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="AK10" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="AL10" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM10" s="23" t="s">
-        <v>110</v>
+        <v>101</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM10" s="30">
+        <v>8801959216012</v>
       </c>
       <c r="AN10" s="14" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19">
+      <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="25" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="7">
@@ -2847,7 +2808,7 @@
       <c r="F11" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="21">
         <v>20260037876</v>
       </c>
       <c r="H11" s="2">
@@ -2862,7 +2823,7 @@
       <c r="K11" s="7">
         <v>35860</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" t="s">
         <v>83</v>
       </c>
       <c r="M11" s="7">
@@ -2871,8 +2832,8 @@
       <c r="N11" s="7">
         <v>49693</v>
       </c>
-      <c r="O11" s="19" t="s">
-        <v>138</v>
+      <c r="O11" t="s">
+        <v>126</v>
       </c>
       <c r="P11" s="7">
         <v>46239</v>
@@ -2880,77 +2841,77 @@
       <c r="Q11" s="7">
         <v>46424</v>
       </c>
-      <c r="S11" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="T11" s="19" t="s">
+      <c r="S11" t="s">
+        <v>115</v>
+      </c>
+      <c r="T11" t="s">
         <v>84</v>
       </c>
-      <c r="U11" s="19" t="s">
+      <c r="U11" t="s">
         <v>86</v>
       </c>
-      <c r="V11" s="19" t="s">
+      <c r="V11" t="s">
         <v>87</v>
       </c>
-      <c r="W11" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="X11" s="19">
+      <c r="W11" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X11">
         <f t="shared" si="0"/>
         <v>20260037876</v>
       </c>
-      <c r="Y11" s="19" t="str">
+      <c r="Y11" t="str">
         <f t="shared" si="1"/>
         <v>MD SAIFUL ISLAM</v>
       </c>
-      <c r="Z11" s="24">
+      <c r="Z11" s="22">
         <f t="shared" si="2"/>
         <v>35860</v>
       </c>
-      <c r="AA11" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC11" s="19" t="str">
+      <c r="AA11" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC11" t="str">
         <f t="shared" si="3"/>
         <v>MD SAIFUL ISLAM</v>
       </c>
-      <c r="AD11" s="19" t="str">
+      <c r="AD11" t="str">
         <f t="shared" si="4"/>
         <v>A09804378</v>
       </c>
-      <c r="AE11" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="AF11" s="19" t="s">
-        <v>124</v>
+      <c r="AE11" t="s">
+        <v>112</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>112</v>
       </c>
       <c r="AG11" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AH11" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AI11" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AJ11" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="AK11" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AL11" t="s">
         <v>89</v>
       </c>
-      <c r="AL11" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM11" s="23" t="s">
-        <v>111</v>
+      <c r="AM11" s="30">
+        <v>8801959216017</v>
       </c>
       <c r="AN11" s="15" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="19">
+      <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -2962,13 +2923,13 @@
       <c r="D12" s="7">
         <v>45947</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="26" t="s">
         <v>52</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="21">
         <v>20260037877</v>
       </c>
       <c r="H12" s="2">
@@ -2983,7 +2944,7 @@
       <c r="K12" s="7">
         <v>39248</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" t="s">
         <v>80</v>
       </c>
       <c r="M12" s="7">
@@ -2992,8 +2953,8 @@
       <c r="N12" s="7">
         <v>49598</v>
       </c>
-      <c r="O12" s="19" t="s">
-        <v>136</v>
+      <c r="O12" t="s">
+        <v>124</v>
       </c>
       <c r="P12" s="7">
         <v>46239</v>
@@ -3001,73 +2962,73 @@
       <c r="Q12" s="7">
         <v>46424</v>
       </c>
-      <c r="S12" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="T12" s="19" t="s">
+      <c r="S12" t="s">
+        <v>115</v>
+      </c>
+      <c r="T12" t="s">
         <v>84</v>
       </c>
-      <c r="U12" s="19" t="s">
+      <c r="U12" t="s">
         <v>86</v>
       </c>
-      <c r="V12" s="19" t="s">
+      <c r="V12" t="s">
         <v>87</v>
       </c>
-      <c r="W12" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="X12" s="19">
+      <c r="W12" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X12">
         <f t="shared" si="0"/>
         <v>20260037877</v>
       </c>
-      <c r="Y12" s="19" t="str">
+      <c r="Y12" t="str">
         <f t="shared" si="1"/>
         <v>MD RAKIB HASSAN</v>
       </c>
-      <c r="Z12" s="24">
+      <c r="Z12" s="22">
         <f t="shared" si="2"/>
         <v>39248</v>
       </c>
-      <c r="AA12" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC12" s="19" t="str">
+      <c r="AA12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC12" t="str">
         <f t="shared" si="3"/>
         <v>MD RAKIB HASSAN</v>
       </c>
-      <c r="AD12" s="19" t="str">
+      <c r="AD12" t="str">
         <f t="shared" si="4"/>
         <v>A20555997</v>
       </c>
-      <c r="AE12" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF12" s="32" t="s">
-        <v>125</v>
+      <c r="AE12" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>113</v>
       </c>
       <c r="AG12" s="12" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="AH12" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI12" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ12" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AK12" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="AL12" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM12" s="30">
+        <v>8801959216022</v>
+      </c>
+      <c r="AN12" s="23" t="s">
         <v>90</v>
-      </c>
-      <c r="AM12" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="AN12" s="25" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1D1657-5055-49EE-BC45-7B07A088E75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49111B0-9806-451D-909F-4C7698E7D405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="167">
   <si>
     <t>SL NO</t>
   </si>
@@ -409,6 +409,126 @@
   </si>
   <si>
     <t>A0938133</t>
+  </si>
+  <si>
+    <t>A15392052</t>
+  </si>
+  <si>
+    <t>MD IBRAHIM MOLLAH</t>
+  </si>
+  <si>
+    <t>A07523685</t>
+  </si>
+  <si>
+    <t>MD NAIM ISLAM</t>
+  </si>
+  <si>
+    <t>A16812261</t>
+  </si>
+  <si>
+    <t>SHAKIL MAHMUD</t>
+  </si>
+  <si>
+    <t>SOHEL AHMED</t>
+  </si>
+  <si>
+    <t>A05210946</t>
+  </si>
+  <si>
+    <t>SOFOR MOLLAH</t>
+  </si>
+  <si>
+    <t>KALPONA BEGUM</t>
+  </si>
+  <si>
+    <t>MD NAZRUL ISLAM</t>
+  </si>
+  <si>
+    <t>MARIYAM AKTER</t>
+  </si>
+  <si>
+    <t>TAJEL MATUBBER</t>
+  </si>
+  <si>
+    <t>MST HASINA BEGUM</t>
+  </si>
+  <si>
+    <t>ABDUS SAMAD</t>
+  </si>
+  <si>
+    <t>JAHANARA BEGUM</t>
+  </si>
+  <si>
+    <t>BAYATI KANDI, HAZRATPUR, KERANIGANJ MODEL, ETAVARA - 1313, DHAKA</t>
+  </si>
+  <si>
+    <t>NAYAKANDA, NAWABGONJ, MASHAIL - 1320, DHAKA</t>
+  </si>
+  <si>
+    <t>DOKHKHIN CHAR KAMAR KANDI, WARD NO- 08,SHIBCHAR, BOHERATOLA - 7930, MADARIPUR</t>
+  </si>
+  <si>
+    <t>BA-68, SOUTH BADDA, BADDA, GULSHAN - 1212, DHAKA</t>
+  </si>
+  <si>
+    <t>KALI MULLAH</t>
+  </si>
+  <si>
+    <t>LIYAKAT ALI</t>
+  </si>
+  <si>
+    <t>SELIM KHAN</t>
+  </si>
+  <si>
+    <t>SOHEL MIA</t>
+  </si>
+  <si>
+    <t>GULSHAN</t>
+  </si>
+  <si>
+    <t>NAWABGONJ</t>
+  </si>
+  <si>
+    <t>KERANIGANJ MODEL</t>
+  </si>
+  <si>
+    <t>ETAVARA</t>
+  </si>
+  <si>
+    <t>MASHAIL</t>
+  </si>
+  <si>
+    <t>BOHERATOLA</t>
+  </si>
+  <si>
+    <t>MADARIPUR</t>
+  </si>
+  <si>
+    <t>SHIBCHAR</t>
+  </si>
+  <si>
+    <t>BAYATI KANDI</t>
+  </si>
+  <si>
+    <t>NAYAKANDA</t>
+  </si>
+  <si>
+    <t>DOKHKHIN CHAR KAMAR KANDI</t>
+  </si>
+  <si>
+    <t>BA-68, SOUTH BADDA</t>
+  </si>
+  <si>
+    <t>A0935887</t>
+  </si>
+  <si>
+    <t>A0935922</t>
+  </si>
+  <si>
+    <t>A0935890</t>
+  </si>
+  <si>
+    <t>A0935899</t>
   </si>
 </sst>
 </file>
@@ -571,7 +691,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -775,8 +895,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76A5AF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1061,6 +1187,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1106,7 +1261,7 @@
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1160,6 +1315,33 @@
     <xf numFmtId="0" fontId="18" fillId="36" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="17" builtinId="30" customBuiltin="1"/>
@@ -1539,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AN12"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -1571,11 +1753,14 @@
     <col min="28" max="28" width="4.5703125" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="36" max="37" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="85" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="99.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1889,26 +2074,26 @@
         <v>8801959216007</v>
       </c>
       <c r="X3">
-        <f t="shared" ref="X3:X12" si="0">G3</f>
+        <f t="shared" ref="X3:X16" si="0">G3</f>
         <v>20260037868</v>
       </c>
       <c r="Y3" t="str">
-        <f t="shared" ref="Y3:Y12" si="1">B3</f>
+        <f t="shared" ref="Y3:Y16" si="1">B3</f>
         <v>RAYHAN KHAN</v>
       </c>
       <c r="Z3" s="22">
-        <f t="shared" ref="Z3:Z12" si="2">K3</f>
+        <f t="shared" ref="Z3:Z16" si="2">K3</f>
         <v>37188</v>
       </c>
       <c r="AA3" t="s">
         <v>91</v>
       </c>
       <c r="AC3" t="str">
-        <f t="shared" ref="AC3:AC12" si="3">Y3</f>
+        <f t="shared" ref="AC3:AC16" si="3">Y3</f>
         <v>RAYHAN KHAN</v>
       </c>
       <c r="AD3" t="str">
-        <f t="shared" ref="AD3:AD12" si="4">C3</f>
+        <f t="shared" ref="AD3:AD16" si="4">C3</f>
         <v>A07322494</v>
       </c>
       <c r="AE3" t="s">
@@ -3029,6 +3214,494 @@
       </c>
       <c r="AN12" s="23" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="7">
+        <v>45064</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" s="21">
+        <v>20260037878</v>
+      </c>
+      <c r="H13" s="2">
+        <v>6010566</v>
+      </c>
+      <c r="I13" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0.67362268518518298</v>
+      </c>
+      <c r="K13" s="7">
+        <v>37300</v>
+      </c>
+      <c r="L13" t="s">
+        <v>80</v>
+      </c>
+      <c r="M13" s="22">
+        <f>D13</f>
+        <v>45064</v>
+      </c>
+      <c r="N13" s="7">
+        <v>48716</v>
+      </c>
+      <c r="O13" t="s">
+        <v>163</v>
+      </c>
+      <c r="P13" s="7">
+        <v>46224</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>46406</v>
+      </c>
+      <c r="S13" t="s">
+        <v>116</v>
+      </c>
+      <c r="T13" t="s">
+        <v>84</v>
+      </c>
+      <c r="U13" t="s">
+        <v>86</v>
+      </c>
+      <c r="V13" t="s">
+        <v>87</v>
+      </c>
+      <c r="W13" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="0"/>
+        <v>20260037878</v>
+      </c>
+      <c r="Y13" t="str">
+        <f t="shared" si="1"/>
+        <v>MD IBRAHIM MOLLAH</v>
+      </c>
+      <c r="Z13" s="22">
+        <f t="shared" si="2"/>
+        <v>37300</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC13" t="str">
+        <f t="shared" si="3"/>
+        <v>MD IBRAHIM MOLLAH</v>
+      </c>
+      <c r="AD13" t="str">
+        <f t="shared" si="4"/>
+        <v>A07523685</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>159</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG13" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="AH13" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI13" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ13" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>147</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM13" s="30">
+        <v>8801959216027</v>
+      </c>
+      <c r="AN13" s="37" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="D14" s="7">
+        <v>45605</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="F14" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="G14" s="21">
+        <v>20260037879</v>
+      </c>
+      <c r="H14" s="2">
+        <v>6010569</v>
+      </c>
+      <c r="I14" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0.71528935185184905</v>
+      </c>
+      <c r="K14" s="7">
+        <v>39334</v>
+      </c>
+      <c r="L14" t="s">
+        <v>82</v>
+      </c>
+      <c r="M14" s="22">
+        <f t="shared" ref="M14:M16" si="5">D14</f>
+        <v>45605</v>
+      </c>
+      <c r="N14" s="7">
+        <v>47430</v>
+      </c>
+      <c r="O14" t="s">
+        <v>164</v>
+      </c>
+      <c r="P14" s="7">
+        <v>46224</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>46405</v>
+      </c>
+      <c r="S14" t="s">
+        <v>116</v>
+      </c>
+      <c r="T14" t="s">
+        <v>84</v>
+      </c>
+      <c r="U14" t="s">
+        <v>86</v>
+      </c>
+      <c r="V14" t="s">
+        <v>87</v>
+      </c>
+      <c r="W14" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="0"/>
+        <v>20260037879</v>
+      </c>
+      <c r="Y14" t="str">
+        <f t="shared" si="1"/>
+        <v>MD NAIM ISLAM</v>
+      </c>
+      <c r="Z14" s="22">
+        <f t="shared" si="2"/>
+        <v>39334</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC14" t="str">
+        <f t="shared" si="3"/>
+        <v>MD NAIM ISLAM</v>
+      </c>
+      <c r="AD14" t="str">
+        <f t="shared" si="4"/>
+        <v>A16812261</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG14" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="AH14" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI14" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ14" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>148</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM14" s="30">
+        <v>8801959216032</v>
+      </c>
+      <c r="AN14" s="38" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="7">
+        <v>45531</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="G15" s="21">
+        <v>20260037880</v>
+      </c>
+      <c r="H15" s="2">
+        <v>6010572</v>
+      </c>
+      <c r="I15" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0.75695601851851502</v>
+      </c>
+      <c r="K15" s="7">
+        <v>37761</v>
+      </c>
+      <c r="L15" t="s">
+        <v>83</v>
+      </c>
+      <c r="M15" s="22">
+        <f t="shared" si="5"/>
+        <v>45531</v>
+      </c>
+      <c r="N15" s="7">
+        <v>49182</v>
+      </c>
+      <c r="O15" t="s">
+        <v>165</v>
+      </c>
+      <c r="P15" s="7">
+        <v>46224</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>46405</v>
+      </c>
+      <c r="S15" t="s">
+        <v>116</v>
+      </c>
+      <c r="T15" t="s">
+        <v>84</v>
+      </c>
+      <c r="U15" t="s">
+        <v>86</v>
+      </c>
+      <c r="V15" t="s">
+        <v>87</v>
+      </c>
+      <c r="W15" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="0"/>
+        <v>20260037880</v>
+      </c>
+      <c r="Y15" t="str">
+        <f t="shared" si="1"/>
+        <v>SHAKIL MAHMUD</v>
+      </c>
+      <c r="Z15" s="22">
+        <f t="shared" si="2"/>
+        <v>37761</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC15" t="str">
+        <f t="shared" si="3"/>
+        <v>SHAKIL MAHMUD</v>
+      </c>
+      <c r="AD15" t="str">
+        <f t="shared" si="4"/>
+        <v>A15392052</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>161</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AG15" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="AH15" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI15" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="AJ15" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM15" s="30">
+        <v>8801959216037</v>
+      </c>
+      <c r="AN15" s="38" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="7">
+        <v>44847</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="G16" s="21">
+        <v>20260037881</v>
+      </c>
+      <c r="H16" s="2">
+        <v>6010575</v>
+      </c>
+      <c r="I16" s="7">
+        <v>46268</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0.79862268518518098</v>
+      </c>
+      <c r="K16" s="7">
+        <v>28659</v>
+      </c>
+      <c r="L16" t="s">
+        <v>80</v>
+      </c>
+      <c r="M16" s="22">
+        <f t="shared" si="5"/>
+        <v>44847</v>
+      </c>
+      <c r="N16" s="7">
+        <v>48499</v>
+      </c>
+      <c r="O16" t="s">
+        <v>166</v>
+      </c>
+      <c r="P16" s="7">
+        <v>46224</v>
+      </c>
+      <c r="Q16" s="7">
+        <v>46405</v>
+      </c>
+      <c r="S16" t="s">
+        <v>116</v>
+      </c>
+      <c r="T16" t="s">
+        <v>84</v>
+      </c>
+      <c r="U16" t="s">
+        <v>86</v>
+      </c>
+      <c r="V16" t="s">
+        <v>87</v>
+      </c>
+      <c r="W16" s="30">
+        <v>8801959216007</v>
+      </c>
+      <c r="X16">
+        <f t="shared" si="0"/>
+        <v>20260037881</v>
+      </c>
+      <c r="Y16" t="str">
+        <f t="shared" si="1"/>
+        <v>SOHEL AHMED</v>
+      </c>
+      <c r="Z16" s="22">
+        <f t="shared" si="2"/>
+        <v>28659</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC16" t="str">
+        <f t="shared" si="3"/>
+        <v>SOHEL AHMED</v>
+      </c>
+      <c r="AD16" t="str">
+        <f t="shared" si="4"/>
+        <v>A05210946</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>162</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>151</v>
+      </c>
+      <c r="AG16" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="AH16" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI16" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ16" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>150</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>89</v>
+      </c>
+      <c r="AM16" s="30">
+        <v>8801959216042</v>
+      </c>
+      <c r="AN16" s="38" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49111B0-9806-451D-909F-4C7698E7D405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BDD5C1-1282-45C6-8469-8BAB224C14B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1261,7 +1261,7 @@
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1342,6 +1342,9 @@
     <xf numFmtId="0" fontId="18" fillId="36" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="36" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="35" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="17" builtinId="30" customBuiltin="1"/>
@@ -1750,7 +1753,7 @@
     <col min="25" max="25" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="13.140625" customWidth="1"/>
     <col min="27" max="27" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="29.7109375" bestFit="1" customWidth="1"/>
@@ -1967,6 +1970,9 @@
       <c r="AA2" t="s">
         <v>91</v>
       </c>
+      <c r="AB2" s="42">
+        <v>3775176872</v>
+      </c>
       <c r="AC2" t="str">
         <f>Y2</f>
         <v>MAMUN HOSEN</v>
@@ -2088,6 +2094,9 @@
       <c r="AA3" t="s">
         <v>91</v>
       </c>
+      <c r="AB3" s="42">
+        <v>8262684908</v>
+      </c>
       <c r="AC3" t="str">
         <f t="shared" ref="AC3:AC16" si="3">Y3</f>
         <v>RAYHAN KHAN</v>
@@ -2209,6 +2218,9 @@
       <c r="AA4" t="s">
         <v>91</v>
       </c>
+      <c r="AB4" s="42">
+        <v>4215410293</v>
+      </c>
       <c r="AC4" t="str">
         <f t="shared" si="3"/>
         <v>MD NAJIM UDDIN</v>
@@ -2330,6 +2342,9 @@
       <c r="AA5" t="s">
         <v>91</v>
       </c>
+      <c r="AB5" s="42">
+        <v>4657003283</v>
+      </c>
       <c r="AC5" t="str">
         <f t="shared" si="3"/>
         <v>RAKIBUL HASAN</v>
@@ -2451,6 +2466,9 @@
       <c r="AA6" t="s">
         <v>91</v>
       </c>
+      <c r="AB6" s="42">
+        <v>5565587135</v>
+      </c>
       <c r="AC6" t="str">
         <f t="shared" si="3"/>
         <v>SUMON AHMED</v>
@@ -2572,6 +2590,9 @@
       <c r="AA7" t="s">
         <v>91</v>
       </c>
+      <c r="AB7" s="42">
+        <v>8252017143</v>
+      </c>
       <c r="AC7" t="str">
         <f t="shared" si="3"/>
         <v>MD SABUJ MIA</v>
@@ -2693,6 +2714,9 @@
       <c r="AA8" t="s">
         <v>91</v>
       </c>
+      <c r="AB8" s="42">
+        <v>3315246417</v>
+      </c>
       <c r="AC8" t="str">
         <f t="shared" si="3"/>
         <v>RASHEL AHMED</v>
@@ -2814,6 +2838,9 @@
       <c r="AA9" t="s">
         <v>91</v>
       </c>
+      <c r="AB9" s="42">
+        <v>3768710950</v>
+      </c>
       <c r="AC9" t="str">
         <f t="shared" si="3"/>
         <v>MD SAKIBUL HASAN MILTON</v>
@@ -2935,6 +2962,9 @@
       <c r="AA10" t="s">
         <v>91</v>
       </c>
+      <c r="AB10" s="42">
+        <v>1980657587</v>
+      </c>
       <c r="AC10" t="str">
         <f t="shared" si="3"/>
         <v>WALID MAHMUD</v>
@@ -3056,6 +3086,9 @@
       <c r="AA11" t="s">
         <v>91</v>
       </c>
+      <c r="AB11" s="42">
+        <v>7355059176</v>
+      </c>
       <c r="AC11" t="str">
         <f t="shared" si="3"/>
         <v>MD SAIFUL ISLAM</v>
@@ -3176,6 +3209,9 @@
       </c>
       <c r="AA12" t="s">
         <v>91</v>
+      </c>
+      <c r="AB12" s="42">
+        <v>3782267995</v>
       </c>
       <c r="AC12" t="str">
         <f t="shared" si="3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BDD5C1-1282-45C6-8469-8BAB224C14B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4D47674-F43F-42A1-AD1C-13895432AF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1261,7 +1261,7 @@
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1342,9 +1342,13 @@
     <xf numFmtId="0" fontId="18" fillId="36" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="36" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="35" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="33" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="17" builtinId="30" customBuiltin="1"/>
@@ -1753,7 +1757,7 @@
     <col min="25" max="25" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="13.140625" customWidth="1"/>
     <col min="27" max="27" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.28515625" style="44" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="29.7109375" bestFit="1" customWidth="1"/>
@@ -1848,7 +1852,7 @@
       <c r="AA1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="AB1" s="11" t="s">
+      <c r="AB1" s="42" t="s">
         <v>69</v>
       </c>
       <c r="AC1" s="11" t="s">
@@ -1970,7 +1974,7 @@
       <c r="AA2" t="s">
         <v>91</v>
       </c>
-      <c r="AB2" s="42">
+      <c r="AB2" s="43">
         <v>3775176872</v>
       </c>
       <c r="AC2" t="str">
@@ -2094,7 +2098,7 @@
       <c r="AA3" t="s">
         <v>91</v>
       </c>
-      <c r="AB3" s="42">
+      <c r="AB3" s="43">
         <v>8262684908</v>
       </c>
       <c r="AC3" t="str">
@@ -2218,7 +2222,7 @@
       <c r="AA4" t="s">
         <v>91</v>
       </c>
-      <c r="AB4" s="42">
+      <c r="AB4" s="43">
         <v>4215410293</v>
       </c>
       <c r="AC4" t="str">
@@ -2342,7 +2346,7 @@
       <c r="AA5" t="s">
         <v>91</v>
       </c>
-      <c r="AB5" s="42">
+      <c r="AB5" s="43">
         <v>4657003283</v>
       </c>
       <c r="AC5" t="str">
@@ -2466,7 +2470,7 @@
       <c r="AA6" t="s">
         <v>91</v>
       </c>
-      <c r="AB6" s="42">
+      <c r="AB6" s="43">
         <v>5565587135</v>
       </c>
       <c r="AC6" t="str">
@@ -2590,7 +2594,7 @@
       <c r="AA7" t="s">
         <v>91</v>
       </c>
-      <c r="AB7" s="42">
+      <c r="AB7" s="43">
         <v>8252017143</v>
       </c>
       <c r="AC7" t="str">
@@ -2714,7 +2718,7 @@
       <c r="AA8" t="s">
         <v>91</v>
       </c>
-      <c r="AB8" s="42">
+      <c r="AB8" s="43">
         <v>3315246417</v>
       </c>
       <c r="AC8" t="str">
@@ -2838,7 +2842,7 @@
       <c r="AA9" t="s">
         <v>91</v>
       </c>
-      <c r="AB9" s="42">
+      <c r="AB9" s="43">
         <v>3768710950</v>
       </c>
       <c r="AC9" t="str">
@@ -2962,7 +2966,7 @@
       <c r="AA10" t="s">
         <v>91</v>
       </c>
-      <c r="AB10" s="42">
+      <c r="AB10" s="43">
         <v>1980657587</v>
       </c>
       <c r="AC10" t="str">
@@ -3086,7 +3090,7 @@
       <c r="AA11" t="s">
         <v>91</v>
       </c>
-      <c r="AB11" s="42">
+      <c r="AB11" s="43">
         <v>7355059176</v>
       </c>
       <c r="AC11" t="str">
@@ -3210,7 +3214,7 @@
       <c r="AA12" t="s">
         <v>91</v>
       </c>
-      <c r="AB12" s="42">
+      <c r="AB12" s="43">
         <v>3782267995</v>
       </c>
       <c r="AC12" t="str">
